--- a/5_evaluation_results/ablation_conditions/2_quality_radar/radar_6axes_datasheet.xlsx
+++ b/5_evaluation_results/ablation_conditions/2_quality_radar/radar_6axes_datasheet.xlsx
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
